--- a/artfynd/A 42022-2021 artfynd.xlsx
+++ b/artfynd/A 42022-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42022-2021 artfynd.xlsx
+++ b/artfynd/A 42022-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82220069</v>
+        <v>82220140</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574595.9437726185</v>
+        <v>574589</v>
       </c>
       <c r="R2" t="n">
-        <v>6568357.070924103</v>
+        <v>6568363</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,19 +743,9 @@
           <t>2019-07-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-07-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,53 +772,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82220066</v>
+        <v>95601501</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stora Uvberget, Srm</t>
+          <t>Nykärret, Näshulta Sn, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574608.1708861928</v>
+        <v>574557</v>
       </c>
       <c r="R3" t="n">
-        <v>6568439.169890815</v>
+        <v>6568516</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +842,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,74 +872,70 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82220068</v>
+        <v>94732042</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Uvberget, Srm</t>
+          <t>Eskilstuna, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574600.2230293805</v>
+        <v>574576</v>
       </c>
       <c r="R4" t="n">
-        <v>6568347.945633262</v>
+        <v>6568415</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +959,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,69 +985,80 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82220081</v>
+        <v>94744424</v>
       </c>
       <c r="B5" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>4368</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Uvberget, Srm</t>
+          <t>Nykärret, Mo, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574599.0701281738</v>
+        <v>574624</v>
       </c>
       <c r="R5" t="n">
-        <v>6568458.944186271</v>
+        <v>6568421</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,22 +1082,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,71 +1106,82 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82220140</v>
+        <v>95601599</v>
       </c>
       <c r="B6" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>4368</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Uvberget, Srm</t>
+          <t>Nykärret, Näshulta Sn, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574589.1630979684</v>
+        <v>574614</v>
       </c>
       <c r="R6" t="n">
-        <v>6568363.077381832</v>
+        <v>6568423</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,22 +1205,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,62 +1235,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>82220132</v>
+        <v>82220040</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>5741</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Uvberget, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574574.1859373512</v>
+        <v>574591</v>
       </c>
       <c r="R7" t="n">
-        <v>6568395.015735917</v>
+        <v>6568429</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1314,22 +1315,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,8 +1329,14 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Johan Svedholm</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1356,53 +1353,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>82220133</v>
+        <v>95601658</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Uvberget, Srm</t>
+          <t>Nykärret, Näshulta Sn, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574608.8724242491</v>
+        <v>574576</v>
       </c>
       <c r="R8" t="n">
-        <v>6568351.18510729</v>
+        <v>6568542</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,22 +1423,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,65 +1453,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>82220067</v>
+        <v>95612267</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Uvberget, Srm</t>
+          <t>Nykärret, Näshulta Sn, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574585.0249967991</v>
+        <v>574553</v>
       </c>
       <c r="R9" t="n">
-        <v>6568391.135398276</v>
+        <v>6568552</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,22 +1535,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,68 +1565,71 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>82220040</v>
+        <v>95601671</v>
       </c>
       <c r="B10" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5741</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Uvberget, Srm</t>
+          <t>Nykärret, Näshulta Sn, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574590.9427205703</v>
+        <v>574576</v>
       </c>
       <c r="R10" t="n">
-        <v>6568429.111177897</v>
+        <v>6568542</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,22 +1653,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-09-03</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-09-03</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,24 +1677,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Johan Svedholm</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1704,12 +1698,7 @@
         <v>82220091</v>
       </c>
       <c r="B11" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574580.8060161752</v>
+        <v>574581</v>
       </c>
       <c r="R11" t="n">
-        <v>6568397.192068508</v>
+        <v>6568397</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1774,19 +1763,9 @@
           <t>2019-07-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-07-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,15 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>82220111</v>
+        <v>94744825</v>
       </c>
       <c r="B12" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,37 +1803,53 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Uvberget, Srm</t>
+          <t>Nykärret, Mo, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574546.1184367235</v>
+        <v>574586</v>
       </c>
       <c r="R12" t="n">
-        <v>6568388.83749187</v>
+        <v>6568394</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,22 +1873,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-09-03</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-09-03</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,81 +1897,67 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>94732042</v>
+        <v>82220066</v>
       </c>
       <c r="B13" t="n">
-        <v>91623</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Eskilstuna, Srm</t>
+          <t>Stora Uvberget, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574576</v>
+        <v>574608</v>
       </c>
       <c r="R13" t="n">
-        <v>6568415</v>
+        <v>6568439</v>
       </c>
       <c r="S13" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2005,22 +1981,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,85 +1997,64 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>94744424</v>
+        <v>82220067</v>
       </c>
       <c r="B14" t="n">
-        <v>91623</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nykärret, Mo, Srm</t>
+          <t>Stora Uvberget, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574624</v>
+        <v>574585</v>
       </c>
       <c r="R14" t="n">
-        <v>6568421</v>
+        <v>6568391</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2133,22 +2078,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,98 +2092,75 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>94744825</v>
+        <v>82220068</v>
       </c>
       <c r="B15" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nykärret, Mo, Srm</t>
+          <t>Stora Uvberget, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574585.4670909701</v>
+        <v>574600</v>
       </c>
       <c r="R15" t="n">
-        <v>6568394.725408496</v>
+        <v>6568348</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2272,22 +2184,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,34 +2198,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>94971520</v>
+        <v>82220069</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,35 +2244,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nykärret, Mo, Näshulta Sn, Srm</t>
+          <t>Stora Uvberget, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574650.8734084904</v>
+        <v>574596</v>
       </c>
       <c r="R16" t="n">
-        <v>6568352.521167206</v>
+        <v>6568357</v>
       </c>
       <c r="S16" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2400,22 +2281,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2430,75 +2301,76 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95601944</v>
+        <v>94744060</v>
       </c>
       <c r="B17" t="n">
-        <v>103252</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>224098</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Eskilstuna, Srm</t>
+          <t>Nykärret, Mo, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574600.2267987592</v>
+        <v>574595</v>
       </c>
       <c r="R17" t="n">
-        <v>6568530.591733929</v>
+        <v>6568430</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2522,22 +2394,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2546,76 +2418,83 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95601658</v>
+        <v>94744236</v>
       </c>
       <c r="B18" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nykärret, Näshulta Sn, Srm</t>
+          <t>Nykärret, Mo, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574575.9076809799</v>
+        <v>574598</v>
       </c>
       <c r="R18" t="n">
-        <v>6568542.39302169</v>
+        <v>6568420</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2639,22 +2518,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,82 +2542,93 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95601671</v>
+        <v>94744333</v>
       </c>
       <c r="B19" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nykärret, Näshulta Sn, Srm</t>
+          <t>Nykärret, Mo, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574575.9076809799</v>
+        <v>574598</v>
       </c>
       <c r="R19" t="n">
-        <v>6568542.39302169</v>
+        <v>6568421</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2762,22 +2652,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2786,76 +2676,93 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>95601501</v>
+        <v>94744388</v>
       </c>
       <c r="B20" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nykärret, Näshulta Sn, Srm</t>
+          <t>Nykärret, Mo, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574556.9415909296</v>
+        <v>574592</v>
       </c>
       <c r="R20" t="n">
-        <v>6568516.440968804</v>
+        <v>6568421</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2879,22 +2786,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,55 +2810,51 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95612267</v>
+        <v>94744407</v>
       </c>
       <c r="B21" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2959,20 +2862,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nykärret, Näshulta Sn, Srm</t>
+          <t>Nykärret, Mo, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574552.6734932436</v>
+        <v>574604</v>
       </c>
       <c r="R21" t="n">
-        <v>6568551.146108606</v>
+        <v>6568432</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2996,22 +2910,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3020,76 +2934,93 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95601599</v>
+        <v>94744544</v>
       </c>
       <c r="B22" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nykärret, Näshulta Sn, Srm</t>
+          <t>Nykärret, Mo, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574614.1275568302</v>
+        <v>574624</v>
       </c>
       <c r="R22" t="n">
-        <v>6568422.915117788</v>
+        <v>6568405</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3113,22 +3044,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ca 50 knärötter inom en yta av 10 m2</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,33 +3073,39 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Äldre mossrik granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>94973490</v>
+        <v>94744567</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3190,26 +3132,34 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nykärret, Mo, Näshulta Sn, Srm</t>
+          <t>Nykärret, Mo, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574661.1601698883</v>
+        <v>574627</v>
       </c>
       <c r="R23" t="n">
-        <v>6568350.676653625</v>
+        <v>6568402</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3233,22 +3183,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-07-10</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-07-10</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3261,30 +3211,35 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Äldre mossig granskog</t>
+        </is>
+      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>94744236</v>
+        <v>94744599</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3311,12 +3266,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3332,10 +3287,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574597.2711700799</v>
+        <v>574632</v>
       </c>
       <c r="R24" t="n">
-        <v>6568420.02626417</v>
+        <v>6568381</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3389,16 +3344,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3415,15 +3360,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>94744407</v>
+        <v>94744680</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3450,7 +3390,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3471,10 +3411,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574604.2128398196</v>
+        <v>574595</v>
       </c>
       <c r="R25" t="n">
-        <v>6568431.929624147</v>
+        <v>6568392</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3536,7 +3476,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre granskog</t>
+          <t>Äldre mossig granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3554,15 +3494,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>94744388</v>
+        <v>94744702</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3610,10 +3545,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574592.1278991553</v>
+        <v>574583</v>
       </c>
       <c r="R26" t="n">
-        <v>6568420.948584362</v>
+        <v>6568393</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3667,6 +3602,16 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3683,15 +3628,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>94744333</v>
+        <v>94744847</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3718,7 +3658,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3728,7 +3668,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>knoppbristning</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3739,10 +3679,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574597.2511011378</v>
+        <v>574586</v>
       </c>
       <c r="R27" t="n">
-        <v>6568421.049102422</v>
+        <v>6568394</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3804,7 +3744,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre granskog</t>
+          <t>Äldre mossig granskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3822,15 +3762,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>94744060</v>
+        <v>94744916</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3857,7 +3792,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3878,10 +3813,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574595.0312391744</v>
+        <v>574633</v>
       </c>
       <c r="R28" t="n">
-        <v>6568429.703008506</v>
+        <v>6568389</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3935,6 +3870,16 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Äldre mossig granskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3951,15 +3896,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>94744680</v>
+        <v>94745070</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3986,7 +3926,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4003,14 +3943,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nykärret, Mo, Srm</t>
+          <t>Nykärret, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574594.7491225925</v>
+        <v>574628</v>
       </c>
       <c r="R29" t="n">
-        <v>6568391.837792782</v>
+        <v>6568384</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4072,7 +4012,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Äldre mossig granskog</t>
+          <t>Äldre granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4093,12 +4033,7 @@
         <v>94745102</v>
       </c>
       <c r="B30" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,10 +4081,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574639.6027187537</v>
+        <v>574639</v>
       </c>
       <c r="R30" t="n">
-        <v>6568404.485325803</v>
+        <v>6568404</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4229,15 +4164,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>94744847</v>
+        <v>94971520</v>
       </c>
       <c r="B31" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4264,7 +4194,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4274,24 +4204,23 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nykärret, Mo, Srm</t>
+          <t>Nykärret, Mo, Näshulta Sn, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574585.4670909701</v>
+        <v>574651</v>
       </c>
       <c r="R31" t="n">
-        <v>6568394.725408496</v>
+        <v>6568353</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4315,22 +4244,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4339,44 +4258,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Äldre mossig granskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>94744916</v>
+        <v>94973490</v>
       </c>
       <c r="B32" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4403,34 +4306,26 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nykärret, Mo, Srm</t>
+          <t>Nykärret, Mo, Näshulta Sn, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574633.7560292295</v>
+        <v>574661</v>
       </c>
       <c r="R32" t="n">
-        <v>6568389.021965972</v>
+        <v>6568350</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4454,22 +4349,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2021-07-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2021-07-10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4482,40 +4367,25 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Äldre mossig granskog</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>94744599</v>
+        <v>101357707</v>
       </c>
       <c r="B33" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4542,34 +4412,30 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nykärret, Mo, Srm</t>
+          <t>Nykärret, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574631.8573172668</v>
+        <v>574607</v>
       </c>
       <c r="R33" t="n">
-        <v>6568381.310379823</v>
+        <v>6568405</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4593,22 +4459,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Holmen skog har kalhuggit ca 35 meter från plantorna.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4617,7 +4488,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4636,15 +4506,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>94744567</v>
+        <v>101358684</v>
       </c>
       <c r="B34" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4671,31 +4536,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nykärret, Mo, Srm</t>
+          <t>Nykärret, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574626.3224877949</v>
+        <v>574581</v>
       </c>
       <c r="R34" t="n">
-        <v>6568402.178159317</v>
+        <v>6568387</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4722,22 +4583,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Holmen skog har avverkat 15 meter från tidigare inrapporterat knärotsbestånd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4746,19 +4612,8 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Äldre mossig granskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4775,69 +4630,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>94744544</v>
+        <v>82220081</v>
       </c>
       <c r="B35" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nykärret, Mo, Srm</t>
+          <t>Stora Uvberget, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574624.7252905762</v>
+        <v>574599</v>
       </c>
       <c r="R35" t="n">
-        <v>6568405.216519942</v>
+        <v>6568459</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4861,27 +4695,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ca 50 knärötter inom en yta av 10 m2</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4890,98 +4709,66 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Äldre mossrik granskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>94745070</v>
+        <v>82220111</v>
       </c>
       <c r="B36" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nykärret, Srm</t>
+          <t>Stora Uvberget, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574627.698481384</v>
+        <v>574546</v>
       </c>
       <c r="R36" t="n">
-        <v>6568384.29847312</v>
+        <v>6568389</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5005,22 +4792,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2019-09-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2019-09-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5029,98 +4806,66 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>94744702</v>
+        <v>82220132</v>
       </c>
       <c r="B37" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nykärret, Mo, Srm</t>
+          <t>Stora Uvberget, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574582.4132134684</v>
+        <v>574574</v>
       </c>
       <c r="R37" t="n">
-        <v>6568393.642261211</v>
+        <v>6568395</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5144,22 +4889,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5168,94 +4903,66 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>101358684</v>
+        <v>82220133</v>
       </c>
       <c r="B38" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nykärret, Srm</t>
+          <t>Stora Uvberget, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574580.5043684685</v>
+        <v>574609</v>
       </c>
       <c r="R38" t="n">
-        <v>6568386.442136438</v>
+        <v>6568351</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5279,27 +4986,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>18:51</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>18:51</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Holmen skog har avverkat 15 meter från tidigare inrapporterat knärotsbestånd.</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5314,77 +5006,70 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>101357707</v>
+        <v>95601944</v>
       </c>
       <c r="B39" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106231</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>224098</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nykärret, Srm</t>
+          <t>Eskilstuna, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574607.3063300609</v>
+        <v>574600</v>
       </c>
       <c r="R39" t="n">
-        <v>6568404.874661334</v>
+        <v>6568531</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5408,27 +5093,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Holmen skog har kalhuggit ca 35 meter från plantorna.</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5443,12 +5123,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 42022-2021 artfynd.xlsx
+++ b/artfynd/A 42022-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82220140</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95601501</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94732042</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744424</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95601599</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82220040</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,6 +1497,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95601658</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1574,6 +1614,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95612267</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1692,6 +1737,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95601671</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1789,6 +1839,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82220091</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1913,6 +1968,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744825</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2010,6 +2070,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82220066</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2107,6 +2172,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82220067</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2213,6 +2283,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82220068</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2310,6 +2385,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82220069</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2434,6 +2514,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744060</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2568,6 +2653,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744236</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2702,6 +2792,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744333</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2826,6 +2921,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744388</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2960,6 +3060,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744407</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3099,6 +3204,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744544</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3233,6 +3343,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744567</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3357,6 +3472,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744599</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3491,6 +3611,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744680</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3625,6 +3750,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744702</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3759,6 +3889,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744847</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3893,6 +4028,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744916</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4027,6 +4167,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94745070</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4161,6 +4306,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94745102</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4273,6 +4423,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94971520</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4379,6 +4534,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94973490</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4503,6 +4663,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101357707</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4627,6 +4792,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101358684</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4724,6 +4894,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82220081</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4821,6 +4996,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82220111</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4918,6 +5098,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82220132</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5015,6 +5200,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82220133</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5132,8 +5322,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95601944</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>